--- a/2024AIDataScienceGNRClub/Advanced Excel/dec21.xlsx
+++ b/2024AIDataScienceGNRClub/Advanced Excel/dec21.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC97088-DB69-4910-911C-67B66BD05A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D31A213-9370-47EE-992C-74AC2A14EFD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{C9233FB1-007A-460A-BFE9-0D2DDFD93EF5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{C9233FB1-007A-460A-BFE9-0D2DDFD93EF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Result" sheetId="2" r:id="rId1"/>
     <sheet name="Marks" sheetId="1" r:id="rId2"/>
-    <sheet name="Functions" sheetId="3" r:id="rId3"/>
+    <sheet name="Ayush Sheth" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
   <si>
     <t>Name</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Last Name</t>
   </si>
   <si>
-    <t>Patel</t>
-  </si>
-  <si>
     <t>First Name</t>
   </si>
   <si>
@@ -210,15 +207,9 @@
     <t>No of students who scored atleast 25 in sub1 but could not score more than 20 in sub2</t>
   </si>
   <si>
-    <t>Total marks of students whose attendance was atleast 70%</t>
-  </si>
-  <si>
     <t>Average Marks per student</t>
   </si>
   <si>
-    <t>Total marks of students whose attendance was atleast 70% &amp; attended independence day</t>
-  </si>
-  <si>
     <t>Average by AVERAGE formula</t>
   </si>
   <si>
@@ -247,6 +238,12 @@
   </si>
   <si>
     <t>Ceil</t>
+  </si>
+  <si>
+    <t>Sum of Total marks of students whose attendance was atleast 70% &amp; attended independence day</t>
+  </si>
+  <si>
+    <t>Sum of Total marks of students whose attendance was atleast 70%</t>
   </si>
 </sst>
 </file>
@@ -604,32 +601,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC079862-F402-4343-9453-1F6205774F5B}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="str">
+        <f>'Ayush Sheth'!B1</f>
+        <v>Ayush Sheth</v>
+      </c>
+      <c r="B2">
         <f>Marks!D7</f>
         <v>45</v>
       </c>
@@ -676,7 +668,7 @@
         <v>13</v>
       </c>
       <c r="K1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L1" t="s">
         <v>15</v>
@@ -714,9 +706,9 @@
       <c r="K2" t="s">
         <v>8</v>
       </c>
-      <c r="L2" t="str">
-        <f>'Final Result'!B2</f>
-        <v>Patel</v>
+      <c r="L2" t="e">
+        <f>'Final Result'!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="M2">
         <f>D7</f>
@@ -887,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1">
         <v>85.39</v>
@@ -904,13 +896,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <f>ROUNDDOWN(G1, 1)</f>
@@ -930,13 +922,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <f>TRUNC(G1, 1)</f>
@@ -956,13 +948,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I4">
         <f>_xlfn.FLOOR.MATH(I1)</f>
@@ -975,7 +967,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="F5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I5">
         <f>_xlfn.CEILING.MATH(I1)</f>
@@ -988,16 +980,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -1008,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>80</v>
@@ -1026,7 +1018,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1044,7 +1036,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>80</v>
@@ -1062,7 +1054,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>88</v>
@@ -1077,7 +1069,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>90</v>
@@ -1095,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>92</v>
@@ -1113,7 +1105,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>88</v>
@@ -1128,7 +1120,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C15">
         <f>COUNT(C7:C13)</f>
@@ -1162,7 +1154,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17">
         <f>C16/$B$4</f>
@@ -1175,7 +1167,7 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C18">
         <f>AVERAGE(C7:C13)</f>
@@ -1188,7 +1180,7 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <f>ROUND(C17, 0)</f>
@@ -1201,7 +1193,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <f>TRUNC(C18, 4)</f>
@@ -1214,7 +1206,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21">
         <f>ROUNDUP(C18, 0)</f>
@@ -1227,7 +1219,7 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22">
         <f>ROUNDDOWN(C18, 0)</f>
@@ -1240,7 +1232,7 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <f>ROUND(C17, -1)</f>
@@ -1249,7 +1241,7 @@
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <f>ROUND(C17, -2)</f>
@@ -1266,59 +1258,60 @@
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="63.109375" customWidth="1"/>
+    <col min="13" max="13" width="77.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s">
         <v>41</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>42</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>43</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>44</v>
-      </c>
-      <c r="E1" t="s">
-        <v>45</v>
       </c>
       <c r="F1" t="s">
         <v>14</v>
       </c>
       <c r="G1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" t="s">
         <v>46</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>47</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>48</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>49</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>50</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>51</v>
-      </c>
-      <c r="M1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1332,7 +1325,7 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <f>B2+C2</f>
+        <f>B2 + C2</f>
         <v>54</v>
       </c>
       <c r="E2">
@@ -1349,18 +1342,18 @@
         <v>55</v>
       </c>
       <c r="I2" t="str">
-        <f>IF(H2&gt;50, "Qualified", "Not Qualified")</f>
-        <v>Qualified</v>
+        <f>IF(H2&gt;=70,"Yes","No")</f>
+        <v>No</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L2">
-        <f>IF(H2&gt;50, F2+$G$2, F2)</f>
-        <v>84</v>
+        <f>IF(H2&gt;=70,F2+$G$2,F2)</f>
+        <v>74</v>
       </c>
       <c r="M2" s="1">
         <f>SUM(J2:J15)</f>
@@ -1375,26 +1368,26 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <f>B3+C3</f>
+        <f t="shared" ref="D3:D6" si="0">B3 + C3</f>
         <v>31</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F15" si="0">D3+E$2</f>
+        <f t="shared" ref="F3:F15" si="1">D3+E$2</f>
         <v>51</v>
       </c>
       <c r="H3">
         <v>68</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I15" si="1">IF(H3&gt;50, "Qualified", "Not Qualified")</f>
-        <v>Qualified</v>
+        <f t="shared" ref="I3:I15" si="2">IF(H3&gt;=70,"Yes","No")</f>
+        <v>No</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L15" si="2">IF(H3&gt;50, F3+$G$2, F3)</f>
-        <v>61</v>
+        <f t="shared" ref="L3:L15" si="3">IF(H3&gt;=70,F3+$G$2,F3)</f>
+        <v>51</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -1408,22 +1401,22 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D15" si="3">B4+C4</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="H4">
         <v>77</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" si="1"/>
-        <v>Qualified</v>
+        <f t="shared" si="2"/>
+        <v>Yes</v>
       </c>
       <c r="L4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>74</v>
       </c>
       <c r="M4" s="1">
@@ -1439,29 +1432,29 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="H5">
         <v>98</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" si="1"/>
-        <v>Qualified</v>
+        <f t="shared" si="2"/>
+        <v>Yes</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="L5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -1475,31 +1468,34 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="H6">
         <v>83</v>
       </c>
       <c r="I6" t="str">
-        <f t="shared" si="1"/>
-        <v>Qualified</v>
+        <f t="shared" si="2"/>
+        <v>Yes</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>87</v>
       </c>
-      <c r="M6" s="1"/>
+      <c r="M6" s="1">
+        <f>COUNT(B2:B15)</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -1509,28 +1505,28 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <f t="shared" si="3"/>
+        <f>B7 + C7</f>
         <v>34</v>
       </c>
       <c r="F7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="H7">
         <v>92</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" si="1"/>
-        <v>Qualified</v>
+        <f t="shared" si="2"/>
+        <v>Yes</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>64</v>
       </c>
       <c r="M7" s="1"/>
@@ -1546,29 +1542,29 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D8:D15" si="4">B8 + C8</f>
         <v>41</v>
       </c>
       <c r="F8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="H8">
         <v>52</v>
       </c>
       <c r="I8" t="str">
-        <f t="shared" si="1"/>
-        <v>Qualified</v>
+        <f t="shared" si="2"/>
+        <v>No</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="L8">
-        <f t="shared" si="2"/>
-        <v>71</v>
+        <f t="shared" si="3"/>
+        <v>61</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -1579,22 +1575,22 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="F9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="H9">
         <v>33</v>
       </c>
       <c r="I9" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Qualified</v>
+        <f t="shared" si="2"/>
+        <v>No</v>
       </c>
       <c r="L9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="M9" s="1">
@@ -1613,32 +1609,32 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="F10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="H10">
         <v>8</v>
       </c>
       <c r="I10" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Qualified</v>
+        <f t="shared" si="2"/>
+        <v>No</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>51</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1652,22 +1648,22 @@
         <v>11</v>
       </c>
       <c r="D11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>37</v>
       </c>
       <c r="F11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="H11">
         <v>42</v>
       </c>
       <c r="I11" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Qualified</v>
+        <f t="shared" si="2"/>
+        <v>No</v>
       </c>
       <c r="L11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>57</v>
       </c>
       <c r="M11" s="1">
@@ -1679,33 +1675,29 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="D12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="F12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="H12">
         <v>49</v>
       </c>
       <c r="I12" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Qualified</v>
+        <f t="shared" si="2"/>
+        <v>No</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1719,29 +1711,29 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>51</v>
       </c>
       <c r="F13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="H13">
         <v>39</v>
       </c>
       <c r="I13" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Qualified</v>
+        <f t="shared" si="2"/>
+        <v>No</v>
       </c>
       <c r="K13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>71</v>
       </c>
       <c r="M13" s="2">
-        <f>COUNTIF(H:H, 8)</f>
+        <f>COUNTIF(H2:H15, 8)</f>
         <v>1</v>
       </c>
     </row>
@@ -1753,32 +1745,32 @@
         <v>29</v>
       </c>
       <c r="D14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="H14">
         <v>90</v>
       </c>
       <c r="I14" t="str">
-        <f t="shared" si="1"/>
-        <v>Qualified</v>
+        <f t="shared" si="2"/>
+        <v>Yes</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>59</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1792,28 +1784,28 @@
         <v>9</v>
       </c>
       <c r="D15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="F15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="H15">
         <v>80</v>
       </c>
       <c r="I15" t="str">
-        <f t="shared" si="1"/>
-        <v>Qualified</v>
+        <f t="shared" si="2"/>
+        <v>Yes</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>59</v>
       </c>
       <c r="M15" s="1">
@@ -1823,7 +1815,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M16" s="1" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -1849,23 +1841,23 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18">
-        <f>$C$17/14</f>
-        <v>19.142857142857142</v>
+        <v>59</v>
+      </c>
+      <c r="D18">
+        <f>ROUND(D17/14, 2)</f>
+        <v>34.14</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19">
-        <f>AVERAGE(C2:C15)</f>
-        <v>24.363636363636363</v>
+        <v>60</v>
+      </c>
+      <c r="D19">
+        <f>ROUND(AVERAGE(D2:D15), 2)</f>
+        <v>36.770000000000003</v>
       </c>
       <c r="M19" s="1">
         <f>SUMIFS(F2:F15, H2:H15, "&gt;=70", J2:J15, 1)</f>
@@ -1874,12 +1866,12 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I24">
         <f>$C$17/14</f>
